--- a/panele-sterowania/Panel-D.xlsx
+++ b/panele-sterowania/Panel-D.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>SYNC CYW 2026-07-04</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -547,7 +547,6 @@
           <t>Zrodlo: gra/data/*.json (15 nacji, roster-6, archetypy Q7=A)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -555,7 +554,6 @@
           <t>Hetyci: archetype_hetyci_nauka_priorytet = 2 (Maciej)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -563,7 +561,6 @@
           <t>Babilonia: nauka +2, wojsko -1 (bez minusa na nauce)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -571,7 +568,6 @@
           <t>Celtowie: Soldurii w bonusy (decyzja CELT)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -579,7 +575,6 @@
           <t>Eksport: CZEKA sygnalu Macieja po edycji Wartosc w Excelu</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -587,7 +582,6 @@
           <t>Ostatni sync: 2026-07-04 22:11</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10820,7 +10814,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Nineveh</t>
+          <t>Arbail</t>
         </is>
       </c>
     </row>

--- a/panele-sterowania/Panel-D.xlsx
+++ b/panele-sterowania/Panel-D.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -477,16 +477,19 @@
           <t>Panel sterowania — Grupa D (Cywilizacje, Dyplomacja, AI, Barbarzyńcy)</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Wygenerowano: 2026-07-04 22:11</t>
-        </is>
-      </c>
+          <t>Wygenerowano: 2026-07-09 18:14</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -494,6 +497,7 @@
           <t>JAK UŻYWAĆ</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -501,6 +505,7 @@
           <t>1. Edytuj kolumnę Wartość (parametry) lub komórki w arkuszach tabelarycznych.</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -508,6 +513,7 @@
           <t>2. Zapisz plik Panel-D.xlsx.</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -515,9 +521,11 @@
           <t>3. Napisz w czacie grupy D: eksportuj panel — agent odpali export-d.py.</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -525,6 +533,7 @@
           <t>Arkusze tabelaryczne: Bonusy-cywilizacji, Cywilizacje-roster, Parametry-cyw, AI-per-nacja, Dyplomacja-akcje, Dyplomacja-per-nacja.</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -532,56 +541,7 @@
           <t>Spec: docs/obieg/PANEL-STEROWANIA-SPEC.md</t>
         </is>
       </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SYNC CYW 2026-07-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Zrodlo: gra/data/*.json (15 nacji, roster-6, archetypy Q7=A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Hetyci: archetype_hetyci_nauka_priorytet = 2 (Maciej)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Babilonia: nauka +2, wojsko -1 (bez minusa na nauce)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Celtowie: Soldurii w bonusy (decyzja CELT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Eksport: CZEKA sygnalu Macieja po edycji Wartosc w Excelu</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ostatni sync: 2026-07-04 22:11</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/panele-sterowania/Panel-D.xlsx
+++ b/panele-sterowania/Panel-D.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Wygenerowano: 2026-07-09 18:14</t>
+          <t>Wygenerowano: 2026-07-09 22:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>

--- a/panele-sterowania/Panel-D.xlsx
+++ b/panele-sterowania/Panel-D.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Wygenerowano: 2026-07-09 22:33</t>
+          <t>Wygenerowano: 2026-07-19 21:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Falanga (Hoplita)</t>
+          <t>Falanga / Wojownik mykeński / Rydwan mykeński / Thorakites</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Legion (Legionista)</t>
+          <t>Hastati / Triari</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Kusznik: +20% ataku i zasięgu łuczników/kuszników (przewaga dystansowa)</t>
+          <t>Łucznicy: +20% ataku i zasięgu jednostek dystansowych (przewaga dystansowa)</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -8484,17 +8484,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>dystans</t>
+          <t>kawaleria</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Kusznik (lepszy łucznik)</t>
+          <t>Jeździec chiński / Halabardnik Shang / Rydwan Shang</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Kusznik = silniejszy łucznik z kuszą; większy zasięg i przebicie pancerza</t>
+          <t>Chińscy specjaliści: Jeździec chiński (kawaleria stepowa), Halabardnik Shang (elitarna piechota), Rydwan Shang (rydwan bojowy)</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Chaska / Królewska Gwardia</t>
+          <t>Wojownik z maczugą (Chaska) / Wojownik z toporem / Procarz (Huaracoc) / Oszczepnik (Estólica) / Gwardzista z champi</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Impi</t>
+          <t>Impi / Oszczepnik Zulu (Izijula) / iButho z iklwa</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Medżaj (Gwardia Faraona)</t>
+          <t>Łucznik egipski / Rydwan egipski / Wojownik z khopesh / Wojownik z żelaznym khopesh</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Gwardia Królewska Sumeru</t>
+          <t>Łucznik sumeryjski / Rydwan sumeryjski / Włócznik sumeryjski / Łucznik akadyjski / Mur tarcz (Sargonid)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Soldurii</t>
+          <t>Soldurii / Rydwan celtycki / Miecznik galijski</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Wojownik germański (framea)</t>
+          <t>Berserker germański</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Strażnik bram Harappy</t>
+          <t>Strażnik bram Harappy / Piechota induska / Garnizon Harappy</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Rydwan Kapadokijski</t>
+          <t>Rydwan Kapadokijski / Piechota hetycka / Gwardia hetycka</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Drużynnik</t>
+          <t>Drużynnik / Jeździec z oszczepami</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Gwardia Ishtar</t>
+          <t>Gwardia Ishtar / Wojownik babiloński / Piechota neobabilońska</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Łucznik asyryjski</t>
+          <t>Konnica lancowa asyryjska / Konnica łucznicza asyryjska / Łucznik asyryjski</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Tyrski miecznik</t>
+          <t>Tyrski miecznik / Wojownik fenicki / Gwardia Tyreńska</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
